--- a/Documento/Consumos.xlsx
+++ b/Documento/Consumos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Womychan\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Soporte\Desktop\PiaDiseno\PiaDiseno\Documento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A0CAC87-B2F8-4BDF-8A09-20AABDE2E518}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200B1F01-E904-4D10-89D7-5BE0A02A0BE5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DCC462A0-CBBD-4C88-84FA-E1CFE167CC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCC462A0-CBBD-4C88-84FA-E1CFE167CC08}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -464,14 +464,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1155C5-487F-4CAF-8649-4A3951E104A1}">
   <dimension ref="A1:E73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.109375" customWidth="1"/>
-    <col min="2" max="2" width="15.21875" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" customWidth="1"/>
+    <col min="2" max="3" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -488,7 +487,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -505,7 +504,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -522,7 +521,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -539,7 +538,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -556,7 +555,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -573,7 +572,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -590,7 +589,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -607,7 +606,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -624,7 +623,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -641,7 +640,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -658,7 +657,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -675,7 +674,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -692,7 +691,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -709,7 +708,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -726,7 +725,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -743,7 +742,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -760,7 +759,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -777,7 +776,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -794,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -811,7 +810,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -828,7 +827,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -845,7 +844,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -862,7 +861,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -879,7 +878,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -896,7 +895,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -913,7 +912,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -930,7 +929,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -947,7 +946,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>10</v>
       </c>
@@ -964,7 +963,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -981,7 +980,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -998,7 +997,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -1015,7 +1014,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>10</v>
       </c>
@@ -1032,7 +1031,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -1049,7 +1048,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>10</v>
       </c>
@@ -1066,7 +1065,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -1083,7 +1082,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>10</v>
       </c>
@@ -1100,7 +1099,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -1117,7 +1116,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>10</v>
       </c>
@@ -1134,7 +1133,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -1151,7 +1150,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>10</v>
       </c>
@@ -1168,7 +1167,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>5</v>
       </c>
@@ -1185,7 +1184,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>10</v>
       </c>
@@ -1202,7 +1201,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>5</v>
       </c>
@@ -1219,7 +1218,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>10</v>
       </c>
@@ -1236,7 +1235,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -1253,7 +1252,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>10</v>
       </c>
@@ -1270,7 +1269,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -1287,7 +1286,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>10</v>
       </c>
@@ -1304,7 +1303,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -1321,7 +1320,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>10</v>
       </c>
@@ -1338,7 +1337,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -1355,7 +1354,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>10</v>
       </c>
@@ -1372,7 +1371,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -1389,7 +1388,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>10</v>
       </c>
@@ -1406,7 +1405,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>5</v>
       </c>
@@ -1423,7 +1422,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -1440,7 +1439,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>5</v>
       </c>
@@ -1457,7 +1456,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>10</v>
       </c>
@@ -1474,7 +1473,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>5</v>
       </c>
@@ -1491,7 +1490,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>10</v>
       </c>
@@ -1508,7 +1507,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>5</v>
       </c>
@@ -1525,7 +1524,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>10</v>
       </c>
@@ -1542,7 +1541,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>5</v>
       </c>
@@ -1559,7 +1558,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>10</v>
       </c>
@@ -1576,7 +1575,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>5</v>
       </c>
@@ -1593,7 +1592,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>10</v>
       </c>
@@ -1610,7 +1609,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>5</v>
       </c>
@@ -1627,7 +1626,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>10</v>
       </c>
@@ -1644,7 +1643,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>5</v>
       </c>
@@ -1661,7 +1660,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>10</v>
       </c>
@@ -1678,7 +1677,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>5</v>
       </c>
@@ -1695,7 +1694,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>10</v>
       </c>
